--- a/database/controller_excel/Resguardo_Janny_Leticia_García_Mendoza.xlsx
+++ b/database/controller_excel/Resguardo_Janny_Leticia_García_Mendoza.xlsx
@@ -47,7 +47,7 @@
     <t>Área:</t>
   </si>
   <si>
-    <t>Base Operativa</t>
+    <t>tf7gy8bu</t>
   </si>
   <si>
     <t>Región:</t>
@@ -59,7 +59,7 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>Ti</t>
+    <t>rc6vtubyin</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>

--- a/database/controller_excel/Resguardo_Janny_Leticia_García_Mendoza.xlsx
+++ b/database/controller_excel/Resguardo_Janny_Leticia_García_Mendoza.xlsx
@@ -47,7 +47,7 @@
     <t>Área:</t>
   </si>
   <si>
-    <t>wwefrtyu</t>
+    <t>w3ert</t>
   </si>
   <si>
     <t>Región:</t>
@@ -59,7 +59,7 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>5esrdft</t>
+    <t>we</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>

--- a/database/controller_excel/Resguardo_Janny_Leticia_García_Mendoza.xlsx
+++ b/database/controller_excel/Resguardo_Janny_Leticia_García_Mendoza.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>21/01/2026</t>
+    <t>06/03/2026</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>w3ert</t>
+    <t>Base Operativa</t>
   </si>
   <si>
     <t>Región:</t>
@@ -59,7 +59,7 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>we</t>
+    <t>T.I</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
@@ -83,28 +83,22 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>Adaptador Tipo C</t>
+    <t>Laptop</t>
   </si>
   <si>
     <t>HP</t>
   </si>
   <si>
-    <t>4g5678l9ñ0</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Adaptador de Corriente</t>
-  </si>
-  <si>
-    <t>KOBLENZ</t>
-  </si>
-  <si>
-    <t>cvbyi</t>
-  </si>
-  <si>
-    <t>VUYBIUNIOMP</t>
+    <t>OMEN</t>
+  </si>
+  <si>
+    <t>YGYEBIBE162878</t>
+  </si>
+  <si>
+    <t>Prueba</t>
+  </si>
+  <si>
+    <t>tbtge</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -134,13 +128,13 @@
     <t>ACEPTA Y RECIBE:</t>
   </si>
   <si>
-    <t>Alejandro Cancino Argüello</t>
-  </si>
-  <si>
-    <t>Coordinador de TI</t>
-  </si>
-  <si>
-    <t>Ingeniero Junior</t>
+    <t>Alejandro Cancino Arguello</t>
+  </si>
+  <si>
+    <t>Coordinador de TI y Telemetría</t>
+  </si>
+  <si>
+    <t>Programador</t>
   </si>
 </sst>
 </file>
@@ -1045,28 +1039,22 @@
         <v>25</v>
       </c>
       <c r="H17" s="53"/>
-      <c r="I17" s="53"/>
+      <c r="I17" s="53" t="s">
+        <v>26</v>
+      </c>
       <c r="J17" s="51"/>
       <c r="K17" s="17"/>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="52"/>
-      <c r="B18" s="53">
-        <v>2</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="53" t="s">
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="53" t="s">
-        <v>28</v>
-      </c>
       <c r="F18" s="53"/>
-      <c r="G18" s="53" t="s">
-        <v>29</v>
-      </c>
+      <c r="G18" s="53"/>
       <c r="H18" s="53"/>
       <c r="I18" s="53"/>
       <c r="J18" s="53"/>
@@ -1111,7 +1099,7 @@
     <row r="22" spans="1:11" customHeight="1" ht="15.75">
       <c r="A22" s="19"/>
       <c r="B22" s="33" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C22" s="26"/>
       <c r="D22" s="26"/>
@@ -1137,7 +1125,7 @@
     <row r="24" spans="1:11" customHeight="1" ht="15.75">
       <c r="A24" s="20"/>
       <c r="B24" s="27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C24" s="26"/>
       <c r="D24" s="26"/>
@@ -1151,7 +1139,7 @@
     <row r="25" spans="1:11" customHeight="1" ht="15">
       <c r="A25" s="20"/>
       <c r="B25" s="27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C25" s="26"/>
       <c r="D25" s="26"/>
@@ -1165,7 +1153,7 @@
     <row r="26" spans="1:11" customHeight="1" ht="15">
       <c r="A26" s="20"/>
       <c r="B26" s="27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C26" s="26"/>
       <c r="D26" s="26"/>
@@ -1179,7 +1167,7 @@
     <row r="27" spans="1:11" customHeight="1" ht="15">
       <c r="A27" s="20"/>
       <c r="B27" s="27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C27" s="26"/>
       <c r="D27" s="26"/>
@@ -1193,7 +1181,7 @@
     <row r="28" spans="1:11" customHeight="1" ht="15">
       <c r="A28" s="20"/>
       <c r="B28" s="27" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C28" s="26"/>
       <c r="D28" s="26"/>
@@ -1219,7 +1207,7 @@
     <row r="30" spans="1:11" customHeight="1" ht="27.75">
       <c r="A30" s="17"/>
       <c r="B30" s="29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C30" s="26"/>
       <c r="D30" s="26"/>
@@ -1251,12 +1239,12 @@
       <c r="A33" s="22"/>
       <c r="B33" s="22"/>
       <c r="C33" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="H33" s="34" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I33" s="26"/>
       <c r="J33" s="26"/>
@@ -1273,7 +1261,7 @@
     <row r="36" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="37" spans="1:11" customHeight="1" ht="15.75">
       <c r="C37" s="25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
@@ -1286,12 +1274,12 @@
     </row>
     <row r="38" spans="1:11" customHeight="1" ht="15.75">
       <c r="C38" s="25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D38" s="26"/>
       <c r="E38" s="26"/>
       <c r="H38" s="25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I38" s="26"/>
       <c r="J38" s="26"/>
